--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][Raw]Aggregated_U_test.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][Raw]Aggregated_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_P2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SD_P1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SD_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Median_P1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Median_P2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Median_difference_P2_minus_P1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -495,40 +507,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C2" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="D2" t="n">
-        <v>8.595797212737683</v>
+        <v>8.692735420989289</v>
       </c>
       <c r="E2" t="n">
-        <v>13.81909113662602</v>
+        <v>13.72591884657598</v>
       </c>
       <c r="F2" t="n">
-        <v>4.000388029704204</v>
+        <v>3.947925656066127</v>
       </c>
       <c r="G2" t="n">
-        <v>3.327929388049815</v>
+        <v>3.320028307872916</v>
       </c>
       <c r="H2" t="n">
-        <v>8.707991198023159</v>
+        <v>8.787739551093544</v>
       </c>
       <c r="I2" t="n">
-        <v>13.8583471264742</v>
+        <v>13.76236711511985</v>
       </c>
       <c r="J2" t="n">
-        <v>5.150355928451042</v>
+        <v>4.974627564026306</v>
       </c>
       <c r="K2" t="n">
-        <v>63097</v>
+        <v>59468</v>
       </c>
       <c r="L2" t="n">
-        <v>7.426984992386937e-91</v>
+        <v>9.583948847275891e-83</v>
       </c>
       <c r="M2" t="n">
-        <v>2.970793996954775e-90</v>
+        <v>3.833579538910356e-82</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -541,40 +553,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C3" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="D3" t="n">
-        <v>70.41336317989327</v>
+        <v>70.37083666829332</v>
       </c>
       <c r="E3" t="n">
-        <v>79.15077528888817</v>
+        <v>79.24804600390699</v>
       </c>
       <c r="F3" t="n">
-        <v>11.20278355231218</v>
+        <v>11.23971097689405</v>
       </c>
       <c r="G3" t="n">
-        <v>7.299581521445715</v>
+        <v>7.261131802111779</v>
       </c>
       <c r="H3" t="n">
-        <v>70.7092248432575</v>
+        <v>70.6402470297961</v>
       </c>
       <c r="I3" t="n">
-        <v>78.73179035587029</v>
+        <v>78.82296778687379</v>
       </c>
       <c r="J3" t="n">
-        <v>8.022565512612786</v>
+        <v>8.182720757077689</v>
       </c>
       <c r="K3" t="n">
-        <v>103982</v>
+        <v>92925</v>
       </c>
       <c r="L3" t="n">
-        <v>4.15033186239949e-43</v>
+        <v>5.17212848623995e-42</v>
       </c>
       <c r="M3" t="n">
-        <v>1.660132744959796e-42</v>
+        <v>2.06885139449598e-41</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -587,40 +599,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C4" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="D4" t="n">
-        <v>11.05467957620632</v>
+        <v>11.15260924739485</v>
       </c>
       <c r="E4" t="n">
-        <v>16.53538555251849</v>
+        <v>16.43532765802524</v>
       </c>
       <c r="F4" t="n">
-        <v>3.712745242037134</v>
+        <v>3.68743080398262</v>
       </c>
       <c r="G4" t="n">
-        <v>3.389310181384221</v>
+        <v>3.392861301117026</v>
       </c>
       <c r="H4" t="n">
-        <v>11.1198201010158</v>
+        <v>11.18056509278695</v>
       </c>
       <c r="I4" t="n">
-        <v>16.724841098689</v>
+        <v>16.595535156915</v>
       </c>
       <c r="J4" t="n">
-        <v>5.605020997673197</v>
+        <v>5.414970064128049</v>
       </c>
       <c r="K4" t="n">
-        <v>55953</v>
+        <v>53458</v>
       </c>
       <c r="L4" t="n">
-        <v>4.781455837603959e-101</v>
+        <v>1.514724309213689e-91</v>
       </c>
       <c r="M4" t="n">
-        <v>1.912582335041584e-100</v>
+        <v>6.058897236854755e-91</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -633,40 +645,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C5" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="D5" t="n">
-        <v>95.86128030757894</v>
+        <v>95.57901474497723</v>
       </c>
       <c r="E5" t="n">
-        <v>80.52570710656649</v>
+        <v>80.94712078189124</v>
       </c>
       <c r="F5" t="n">
-        <v>25.91245674254677</v>
+        <v>26.14354482605308</v>
       </c>
       <c r="G5" t="n">
-        <v>30.61996967182334</v>
+        <v>30.78547802187492</v>
       </c>
       <c r="H5" t="n">
-        <v>98.74895763127256</v>
+        <v>98.2102460020832</v>
       </c>
       <c r="I5" t="n">
-        <v>82.40698103670115</v>
+        <v>83.10362110164814</v>
       </c>
       <c r="J5" t="n">
-        <v>-16.34197659457141</v>
+        <v>-15.10662490043505</v>
       </c>
       <c r="K5" t="n">
-        <v>247095</v>
+        <v>220681</v>
       </c>
       <c r="L5" t="n">
-        <v>1.269277796470854e-18</v>
+        <v>3.912274477239364e-16</v>
       </c>
       <c r="M5" t="n">
-        <v>5.077111185883416e-18</v>
+        <v>1.564909790895746e-15</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
